--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-23 19:21:50</t>
+    <t xml:space="preserve">2026-01-25 19:33:25</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>
@@ -582,13 +582,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006873</v>
+        <v>0.007218</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03961</v>
+        <v>0.040234</v>
       </c>
       <c r="E2" t="n">
-        <v>2152.76</v>
+        <v>2355.39</v>
       </c>
       <c r="F2" t="n">
         <v>1000</v>
@@ -605,10 +605,10 @@
         <v>0.000022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003504</v>
+        <v>0.003502</v>
       </c>
       <c r="E3" t="n">
-        <v>4327.01</v>
+        <v>4161.3</v>
       </c>
       <c r="F3" t="n">
         <v>1000</v>
@@ -625,10 +625,10 @@
         <v>0.000034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004315</v>
+        <v>0.004313</v>
       </c>
       <c r="E4" t="n">
-        <v>4071.37</v>
+        <v>4006.07</v>
       </c>
       <c r="F4" t="n">
         <v>1000</v>
@@ -642,13 +642,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000364</v>
+        <v>0.000363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01345</v>
+        <v>0.013432</v>
       </c>
       <c r="E5" t="n">
-        <v>1567.41</v>
+        <v>1291.18</v>
       </c>
       <c r="F5" t="n">
         <v>1000</v>
@@ -665,10 +665,10 @@
         <v>0.001118</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024292</v>
+        <v>0.02429</v>
       </c>
       <c r="E6" t="n">
-        <v>-728.38</v>
+        <v>-598.72</v>
       </c>
       <c r="F6" t="n">
         <v>1000</v>
@@ -685,10 +685,10 @@
         <v>0.000098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007646</v>
+        <v>0.00765</v>
       </c>
       <c r="E7" t="n">
-        <v>2682.96</v>
+        <v>2654.54</v>
       </c>
       <c r="F7" t="n">
         <v>1000</v>
@@ -742,10 +742,10 @@
         <v>0.000355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.011491</v>
+        <v>0.011492</v>
       </c>
       <c r="F2" t="n">
-        <v>-3302.41</v>
+        <v>-3454.43</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -762,13 +762,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.032304</v>
+        <v>0.03404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.133165</v>
+        <v>0.136456</v>
       </c>
       <c r="F3" t="n">
-        <v>5659.42</v>
+        <v>5671.75</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -788,10 +788,10 @@
         <v>0.000354</v>
       </c>
       <c r="E4" t="n">
-        <v>0.011486</v>
+        <v>0.011487</v>
       </c>
       <c r="F4" t="n">
-        <v>3601.57</v>
+        <v>3627.53</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -808,13 +808,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000371</v>
+        <v>0.000369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01183</v>
+        <v>0.011785</v>
       </c>
       <c r="F5" t="n">
-        <v>4190.73</v>
+        <v>4235.91</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -834,10 +834,10 @@
         <v>0.000354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.011477</v>
+        <v>0.01148</v>
       </c>
       <c r="F6" t="n">
-        <v>4307.76</v>
+        <v>4284.77</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -995,19 +995,19 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000220510840146664</v>
+        <v>0.000022072815914142</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00349987101066586</v>
+        <v>0.00350164442843429</v>
       </c>
       <c r="F2" t="n">
-        <v>6118.37105675463</v>
+        <v>6197.99496720381</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -1024,13 +1024,13 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000220798021771321</v>
+        <v>0.0000220758286778471</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00350035100103924</v>
+        <v>0.00350031624878505</v>
       </c>
       <c r="F3" t="n">
-        <v>-1110.60395619706</v>
+        <v>-1853.31135892352</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1041,19 +1041,19 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000221493745717122</v>
+        <v>0.0000221028496511079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00350754493015052</v>
+        <v>0.00350398158196061</v>
       </c>
       <c r="F4" t="n">
-        <v>6230.29599769596</v>
+        <v>6149.66082564719</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1070,13 +1070,13 @@
         <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000221851439955279</v>
+        <v>0.0000221142231310187</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00350680323984356</v>
+        <v>0.00350130435394098</v>
       </c>
       <c r="F5" t="n">
-        <v>6069.98902615671</v>
+        <v>6150.84566075275</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1093,13 +1093,13 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000343156412396789</v>
+        <v>0.0000342891762629105</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00431129651580529</v>
+        <v>0.00430715491474091</v>
       </c>
       <c r="F6" t="n">
-        <v>5508.82107023185</v>
+        <v>5621.62603480591</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1110,19 +1110,19 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000343200108530477</v>
+        <v>0.0000343323132413725</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00431433767241921</v>
+        <v>0.00431244834374611</v>
       </c>
       <c r="F7" t="n">
-        <v>5925.88590484404</v>
+        <v>5513.45412415785</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
@@ -1133,19 +1133,19 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000343276839267905</v>
+        <v>0.0000343548762962215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00431332375458778</v>
+        <v>0.00431465842523526</v>
       </c>
       <c r="F8" t="n">
-        <v>5567.2927690699</v>
+        <v>5906.117566007</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -1162,13 +1162,13 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000345066273748728</v>
+        <v>0.000034504478514368</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00431960424717923</v>
+        <v>0.00431956984664171</v>
       </c>
       <c r="F9" t="n">
-        <v>-716.518997323849</v>
+        <v>-1016.93395371286</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -1185,13 +1185,13 @@
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000979807917381879</v>
+        <v>0.000097968589463147</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00761451440952866</v>
+        <v>0.007610469739582</v>
       </c>
       <c r="F10" t="n">
-        <v>4657.27240128892</v>
+        <v>4678.15826661324</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -1208,13 +1208,13 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000980385491302219</v>
+        <v>0.0000982091782302409</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00761701534631719</v>
+        <v>0.00764416773516557</v>
       </c>
       <c r="F11" t="n">
-        <v>4849.18960719136</v>
+        <v>4798.44491601081</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-01-25 19:33:25</t>
+    <t xml:space="preserve">2026-02-01 22:55:41</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>
@@ -582,13 +582,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007218</v>
+        <v>0.000514</v>
       </c>
       <c r="D2" t="n">
-        <v>0.040234</v>
+        <v>0.016207</v>
       </c>
       <c r="E2" t="n">
-        <v>2355.39</v>
+        <v>1840.35</v>
       </c>
       <c r="F2" t="n">
         <v>1000</v>
@@ -608,7 +608,7 @@
         <v>0.003502</v>
       </c>
       <c r="E3" t="n">
-        <v>4161.3</v>
+        <v>4403.34</v>
       </c>
       <c r="F3" t="n">
         <v>1000</v>
@@ -625,10 +625,10 @@
         <v>0.000034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004313</v>
+        <v>0.004314</v>
       </c>
       <c r="E4" t="n">
-        <v>4006.07</v>
+        <v>4056.43</v>
       </c>
       <c r="F4" t="n">
         <v>1000</v>
@@ -642,13 +642,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000363</v>
+        <v>0.000364</v>
       </c>
       <c r="D5" t="n">
-        <v>0.013432</v>
+        <v>0.013447</v>
       </c>
       <c r="E5" t="n">
-        <v>1291.18</v>
+        <v>1446.07</v>
       </c>
       <c r="F5" t="n">
         <v>1000</v>
@@ -665,10 +665,10 @@
         <v>0.001118</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02429</v>
+        <v>0.024296</v>
       </c>
       <c r="E6" t="n">
-        <v>-598.72</v>
+        <v>-810.97</v>
       </c>
       <c r="F6" t="n">
         <v>1000</v>
@@ -685,10 +685,10 @@
         <v>0.000098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00765</v>
+        <v>0.007645</v>
       </c>
       <c r="E7" t="n">
-        <v>2654.54</v>
+        <v>2836.25</v>
       </c>
       <c r="F7" t="n">
         <v>1000</v>
@@ -745,7 +745,7 @@
         <v>0.011492</v>
       </c>
       <c r="F2" t="n">
-        <v>-3454.43</v>
+        <v>-3208.69</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -762,13 +762,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03404</v>
+        <v>0.000508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.136456</v>
+        <v>0.01613</v>
       </c>
       <c r="F3" t="n">
-        <v>5671.75</v>
+        <v>3535.26</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -788,10 +788,10 @@
         <v>0.000354</v>
       </c>
       <c r="E4" t="n">
-        <v>0.011487</v>
+        <v>0.011483</v>
       </c>
       <c r="F4" t="n">
-        <v>3627.53</v>
+        <v>3617.62</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -808,13 +808,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000369</v>
+        <v>0.000372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.011785</v>
+        <v>0.011835</v>
       </c>
       <c r="F5" t="n">
-        <v>4235.91</v>
+        <v>4202.79</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -834,10 +834,10 @@
         <v>0.000354</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01148</v>
+        <v>0.011478</v>
       </c>
       <c r="F6" t="n">
-        <v>4284.77</v>
+        <v>4286.78</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1001,13 +1001,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000022072815914142</v>
+        <v>0.0000220734883384139</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00350164442843429</v>
+        <v>0.0034986759293063</v>
       </c>
       <c r="F2" t="n">
-        <v>6197.99496720381</v>
+        <v>6236.36806595074</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -1024,13 +1024,13 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000220758286778471</v>
+        <v>0.0000220780623595792</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00350031624878505</v>
+        <v>0.00350005998084207</v>
       </c>
       <c r="F3" t="n">
-        <v>-1853.31135892352</v>
+        <v>-841.128167265488</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1047,13 +1047,13 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000221028496511079</v>
+        <v>0.0000221125950961247</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00350398158196061</v>
+        <v>0.00350258090010257</v>
       </c>
       <c r="F4" t="n">
-        <v>6149.66082564719</v>
+        <v>6126.97657444797</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1070,13 +1070,13 @@
         <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000221142231310187</v>
+        <v>0.0000221586308442225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00350130435394098</v>
+        <v>0.00350657522709918</v>
       </c>
       <c r="F5" t="n">
-        <v>6150.84566075275</v>
+        <v>6091.12355668695</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1087,19 +1087,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000342891762629105</v>
+        <v>0.0000342879023770953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00430715491474091</v>
+        <v>0.00430993310253984</v>
       </c>
       <c r="F6" t="n">
-        <v>5621.62603480591</v>
+        <v>5898.69094610072</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1116,13 +1116,13 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000343323132413725</v>
+        <v>0.0000343134264060025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00431244834374611</v>
+        <v>0.00431232536809715</v>
       </c>
       <c r="F7" t="n">
-        <v>5513.45412415785</v>
+        <v>5499.50128709555</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
@@ -1133,19 +1133,19 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0000343548762962215</v>
+        <v>0.000034380430021123</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00431465842523526</v>
+        <v>0.00431437218736813</v>
       </c>
       <c r="F8" t="n">
-        <v>5906.117566007</v>
+        <v>5568.48559558248</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -1162,13 +1162,13 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000034504478514368</v>
+        <v>0.00003450217978867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00431956984664171</v>
+        <v>0.00431935149035112</v>
       </c>
       <c r="F9" t="n">
-        <v>-1016.93395371286</v>
+        <v>-740.941689798181</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -1179,19 +1179,19 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000097968589463147</v>
+        <v>0.0000978526990960806</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007610469739582</v>
+        <v>0.00761288363878511</v>
       </c>
       <c r="F10" t="n">
-        <v>4678.15826661324</v>
+        <v>4844.06105502113</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -1202,19 +1202,19 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000982091782302409</v>
+        <v>0.000097933010840291</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00764416773516557</v>
+        <v>0.00761151151521311</v>
       </c>
       <c r="F11" t="n">
-        <v>4798.44491601081</v>
+        <v>4578.68296307645</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -33,19 +33,19 @@
     <t xml:space="preserve">Successful Fits</t>
   </si>
   <si>
-    <t xml:space="preserve">25</t>
+    <t xml:space="preserve">19</t>
   </si>
   <si>
     <t xml:space="preserve">Success Rate (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">83.3</t>
+    <t xml:space="preserve">63.3</t>
   </si>
   <si>
     <t xml:space="preserve">Failed Models</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">11</t>
   </si>
   <si>
     <t xml:space="preserve">Assets Processed</t>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-01 22:55:41</t>
+    <t xml:space="preserve">2026-02-04 10:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>
@@ -114,25 +114,28 @@
     <t xml:space="preserve">TGARCH</t>
   </si>
   <si>
+    <t xml:space="preserve">std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eGARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gjrGARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sGARCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SplitType</t>
+  </si>
+  <si>
     <t xml:space="preserve">sstd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gjrGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sGARCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">norm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SplitType</t>
   </si>
   <si>
     <t xml:space="preserve">Optimization convergence failure (code 52)</t>
@@ -579,16 +582,16 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000514</v>
+        <v>0.000517</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016207</v>
+        <v>0.016282</v>
       </c>
       <c r="E2" t="n">
-        <v>1840.35</v>
+        <v>1355.85</v>
       </c>
       <c r="F2" t="n">
         <v>1000</v>
@@ -599,16 +602,16 @@
         <v>23</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>0.000022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003502</v>
+        <v>0.003503</v>
       </c>
       <c r="E3" t="n">
-        <v>4403.34</v>
+        <v>3701.14</v>
       </c>
       <c r="F3" t="n">
         <v>1000</v>
@@ -619,16 +622,16 @@
         <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>0.000034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004314</v>
+        <v>0.004316</v>
       </c>
       <c r="E4" t="n">
-        <v>4056.43</v>
+        <v>3555.83</v>
       </c>
       <c r="F4" t="n">
         <v>1000</v>
@@ -639,16 +642,16 @@
         <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000364</v>
+        <v>0.000366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.013447</v>
+        <v>0.013498</v>
       </c>
       <c r="E5" t="n">
-        <v>1446.07</v>
+        <v>908.89</v>
       </c>
       <c r="F5" t="n">
         <v>1000</v>
@@ -659,16 +662,16 @@
         <v>26</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001118</v>
+        <v>0.00112</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024296</v>
+        <v>0.024302</v>
       </c>
       <c r="E6" t="n">
-        <v>-810.97</v>
+        <v>-1915.43</v>
       </c>
       <c r="F6" t="n">
         <v>1000</v>
@@ -679,16 +682,16 @@
         <v>27</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0.000098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007645</v>
+        <v>0.007658</v>
       </c>
       <c r="E7" t="n">
-        <v>2836.25</v>
+        <v>2213.2</v>
       </c>
       <c r="F7" t="n">
         <v>1000</v>
@@ -745,7 +748,7 @@
         <v>0.011492</v>
       </c>
       <c r="F2" t="n">
-        <v>-3208.69</v>
+        <v>-3269.7</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -762,13 +765,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000508</v>
+        <v>0.000506</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01613</v>
+        <v>0.016093</v>
       </c>
       <c r="F3" t="n">
-        <v>3535.26</v>
+        <v>3529.32</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -788,10 +791,10 @@
         <v>0.000354</v>
       </c>
       <c r="E4" t="n">
-        <v>0.011483</v>
+        <v>0.011485</v>
       </c>
       <c r="F4" t="n">
-        <v>3617.62</v>
+        <v>3614.41</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -817,29 +820,6 @@
         <v>4202.79</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.000354</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.011478</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4286.78</v>
-      </c>
-      <c r="G6" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -879,13 +859,13 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -896,13 +876,13 @@
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -913,13 +893,13 @@
         <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -930,13 +910,13 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -947,13 +927,13 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -978,16 +958,16 @@
         <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
@@ -995,19 +975,19 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000220734883384139</v>
+        <v>0.0000220806815155538</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0034986759293063</v>
+        <v>0.00350059548461617</v>
       </c>
       <c r="F2" t="n">
-        <v>6236.36806595074</v>
+        <v>-1211.44723357436</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -1018,19 +998,19 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000220780623595792</v>
+        <v>0.0000220899886058771</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00350005998084207</v>
+        <v>0.00350315431501287</v>
       </c>
       <c r="F3" t="n">
-        <v>-841.128167265488</v>
+        <v>6223.74448177264</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1044,16 +1024,16 @@
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000221125950961247</v>
+        <v>0.0000221586308442225</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00350258090010257</v>
+        <v>0.00350657522709918</v>
       </c>
       <c r="F4" t="n">
-        <v>6126.97657444797</v>
+        <v>6091.12355668695</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
@@ -1061,22 +1041,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.0000342964198041262</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00431375960712445</v>
       </c>
       <c r="F5" t="n">
-        <v>6091.12355668695</v>
+        <v>5902.8244011558</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1087,19 +1067,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000342879023770953</v>
+        <v>0.000034380430021123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00430993310253984</v>
+        <v>0.00431437218736813</v>
       </c>
       <c r="F6" t="n">
-        <v>5898.69094610072</v>
+        <v>5568.48559558248</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
@@ -1110,19 +1090,19 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000343134264060025</v>
+        <v>0.0000345046057821764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00431232536809715</v>
+        <v>0.00431957891814382</v>
       </c>
       <c r="F7" t="n">
-        <v>5499.50128709555</v>
+        <v>-803.811410289445</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
@@ -1130,22 +1110,22 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.000098089951593645</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.00761853085890284</v>
       </c>
       <c r="F8" t="n">
-        <v>5568.48559558248</v>
+        <v>4861.56207368077</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -1153,22 +1133,22 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00003450217978867</v>
+        <v>0.0000985129890248958</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00431935149035112</v>
+        <v>0.00767487245432214</v>
       </c>
       <c r="F9" t="n">
-        <v>-740.941689798181</v>
+        <v>4597.28223830732</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -1179,19 +1159,19 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000978526990960806</v>
+        <v>0.0000985764594588027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00761288363878511</v>
+        <v>0.00768124969168561</v>
       </c>
       <c r="F10" t="n">
-        <v>4844.06105502113</v>
+        <v>-2819.25534825357</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -1199,22 +1179,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000097933010840291</v>
+        <v>0.000357402335537457</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00761151151521311</v>
+        <v>0.0133117347345129</v>
       </c>
       <c r="F11" t="n">
-        <v>4578.68296307645</v>
+        <v>3037.58715489622</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-04 10:41:46</t>
+    <t xml:space="preserve">2026-02-04 16:30:49</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>
@@ -585,16 +585,16 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000517</v>
+        <v>0.000531</v>
       </c>
       <c r="D2" t="n">
-        <v>0.016282</v>
+        <v>0.01661</v>
       </c>
       <c r="E2" t="n">
-        <v>1355.85</v>
+        <v>2270.73</v>
       </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -608,13 +608,13 @@
         <v>0.000022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003503</v>
+        <v>0.003511</v>
       </c>
       <c r="E3" t="n">
-        <v>3701.14</v>
+        <v>4784.14</v>
       </c>
       <c r="F3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -628,13 +628,13 @@
         <v>0.000034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004316</v>
+        <v>0.004327</v>
       </c>
       <c r="E4" t="n">
-        <v>3555.83</v>
+        <v>4508.04</v>
       </c>
       <c r="F4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -648,13 +648,13 @@
         <v>0.000366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.013498</v>
+        <v>0.013494</v>
       </c>
       <c r="E5" t="n">
-        <v>908.89</v>
+        <v>1964.46</v>
       </c>
       <c r="F5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -665,16 +665,16 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00112</v>
+        <v>0.001121</v>
       </c>
       <c r="D6" t="n">
-        <v>0.024302</v>
+        <v>0.024319</v>
       </c>
       <c r="E6" t="n">
-        <v>-1915.43</v>
+        <v>-237.39</v>
       </c>
       <c r="F6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -685,16 +685,16 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000098</v>
+        <v>0.000099</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007658</v>
+        <v>0.007673</v>
       </c>
       <c r="E7" t="n">
-        <v>2213.2</v>
+        <v>3290.62</v>
       </c>
       <c r="F7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -748,10 +748,10 @@
         <v>0.011492</v>
       </c>
       <c r="F2" t="n">
-        <v>-3269.7</v>
+        <v>213.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -765,16 +765,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000506</v>
+        <v>0.000553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.016093</v>
+        <v>0.017236</v>
       </c>
       <c r="F3" t="n">
-        <v>3529.32</v>
+        <v>3496.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -788,16 +788,16 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000354</v>
+        <v>0.000355</v>
       </c>
       <c r="E4" t="n">
-        <v>0.011485</v>
+        <v>0.011513</v>
       </c>
       <c r="F4" t="n">
-        <v>3614.41</v>
+        <v>3813.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -814,13 +814,13 @@
         <v>0.000372</v>
       </c>
       <c r="E5" t="n">
-        <v>0.011835</v>
+        <v>0.011857</v>
       </c>
       <c r="F5" t="n">
-        <v>4202.79</v>
+        <v>4058.42</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -981,16 +981,16 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0000220806815155538</v>
+        <v>0.0000220786970132616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00350059548461617</v>
+        <v>0.0035002379434319</v>
       </c>
       <c r="F2" t="n">
-        <v>-1211.44723357436</v>
+        <v>2253.61726177711</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -998,22 +998,22 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000220899886058771</v>
+        <v>0.0000221502614205928</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00350315431501287</v>
+        <v>0.00350098170754738</v>
       </c>
       <c r="F3" t="n">
-        <v>6223.74448177264</v>
+        <v>5964.7368220389</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1021,22 +1021,22 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0000221586308442225</v>
+        <v>0.0000223615885486666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00350657522709918</v>
+        <v>0.00353185265624556</v>
       </c>
       <c r="F4" t="n">
-        <v>6091.12355668695</v>
+        <v>6134.05590876226</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1050,16 +1050,16 @@
         <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0000342964198041262</v>
+        <v>0.0000344300611238395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00431375960712445</v>
+        <v>0.0043345000740643</v>
       </c>
       <c r="F5" t="n">
-        <v>5902.8244011558</v>
+        <v>5835.55752941045</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1067,22 +1067,22 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000034380430021123</v>
+        <v>0.0000345013235870406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00431437218736813</v>
+        <v>0.00431928121262559</v>
       </c>
       <c r="F6" t="n">
-        <v>5568.48559558248</v>
+        <v>2341.25927651771</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1090,22 +1090,22 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000345046057821764</v>
+        <v>0.0000345178681459439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00431957891814382</v>
+        <v>0.00432795002506048</v>
       </c>
       <c r="F7" t="n">
-        <v>-803.811410289445</v>
+        <v>5347.30986735</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1119,16 +1119,16 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000098089951593645</v>
+        <v>0.000097968623664851</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00761853085890284</v>
+        <v>0.00762478844455467</v>
       </c>
       <c r="F8" t="n">
-        <v>4861.56207368077</v>
+        <v>4771.47952131575</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1136,22 +1136,22 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0000985129890248958</v>
+        <v>0.0000985475241770422</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00767487245432214</v>
+        <v>0.00768033438730387</v>
       </c>
       <c r="F9" t="n">
-        <v>4597.28223830732</v>
+        <v>621.379306545768</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1159,22 +1159,22 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0000985764594588027</v>
+        <v>0.0000993909985205136</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00768124969168561</v>
+        <v>0.00771464216274853</v>
       </c>
       <c r="F10" t="n">
-        <v>-2819.25534825357</v>
+        <v>4479.01481686913</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1188,16 +1188,16 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000357402335537457</v>
+        <v>0.000356706471914379</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0133117347345129</v>
+        <v>0.0132974872468535</v>
       </c>
       <c r="F11" t="n">
-        <v>3037.58715489622</v>
+        <v>3197.58996884358</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-04 16:30:49</t>
+    <t xml:space="preserve">2026-02-05 07:16:45</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-05 07:16:45</t>
+    <t xml:space="preserve">2026-02-05 18:58:15</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-05 18:58:15</t>
+    <t xml:space="preserve">2026-02-06 17:29:56</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-06 17:29:56</t>
+    <t xml:space="preserve">2026-02-07 04:49:13</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-07 04:49:13</t>
+    <t xml:space="preserve">2026-02-07 22:13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-07 22:13:59</t>
+    <t xml:space="preserve">2026-02-10 22:53:03</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-10 22:53:03</t>
+    <t xml:space="preserve">2026-02-14 08:31:07</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>

--- a/results/consolidated/Analysis_Summary.xlsx
+++ b/results/consolidated/Analysis_Summary.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Analysis Date</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-14 08:31:07</t>
+    <t xml:space="preserve">2026-04-12 05:36:28</t>
   </si>
   <si>
     <t xml:space="preserve">Asset</t>
